--- a/Obszar testowy/Awaryjność/kalkulacja Blanc PRO.xlsx
+++ b/Obszar testowy/Awaryjność/kalkulacja Blanc PRO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ReportsBI\Obszar testowy\Awaryjność\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3596D43E-3089-4AC8-9FBC-29DF9A57E14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FC7A11-F9EA-41AF-A12F-FD7092598FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1920" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="źródła danych" sheetId="8" r:id="rId1"/>
@@ -1971,7 +1971,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2056,6 +2056,54 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -2121,7 +2169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2191,13 +2239,7 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2280,6 +2322,23 @@
     <xf numFmtId="166" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -3150,7 +3209,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>-1.1131724399994394</c:v>
+                  <c:v>-0.77652878949899629</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.66177991091223221</c:v>
@@ -7082,7 +7141,7 @@
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7092,15 +7151,15 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="83" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="81" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
@@ -7111,7 +7170,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="82" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
@@ -7122,7 +7181,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="82" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
@@ -7133,7 +7192,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="82" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
@@ -7144,7 +7203,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="82" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
@@ -7155,7 +7214,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="82" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
@@ -7166,7 +7225,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="82" t="s">
         <v>19</v>
       </c>
       <c r="B11" t="s">
@@ -7177,7 +7236,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="82" t="s">
         <v>20</v>
       </c>
       <c r="B12" t="s">
@@ -7212,15 +7271,15 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="83" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="82" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
@@ -7231,7 +7290,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -7244,10 +7303,10 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="85" t="s">
+      <c r="A45" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="85" t="s">
+      <c r="B45" s="83" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7347,10 +7406,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="80" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="10" t="s">
@@ -7368,25 +7427,25 @@
       <c r="G1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="H1" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="82" t="s">
+      <c r="I1" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="82" t="s">
+      <c r="J1" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="82" t="s">
+      <c r="K1" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="82" t="s">
+      <c r="L1" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="82" t="s">
+      <c r="M1" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="82" t="s">
+      <c r="N1" s="80" t="s">
         <v>20</v>
       </c>
       <c r="O1" s="9" t="s">
@@ -7878,10 +7937,10 @@
       <c r="G11" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="H11" s="99" t="s">
+      <c r="H11" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="99" t="s">
+      <c r="I11" s="97" t="s">
         <v>242</v>
       </c>
       <c r="J11" s="2" t="s">
@@ -7929,10 +7988,10 @@
       <c r="G12" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="H12" s="99" t="s">
+      <c r="H12" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="I12" s="99" t="s">
+      <c r="I12" s="97" t="s">
         <v>242</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -12337,7 +12396,7 @@
         <v>521</v>
       </c>
       <c r="C9" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -12819,14 +12878,14 @@
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="31.28515625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="23.85546875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="24" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="31.28515625" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -12931,8 +12990,8 @@
       <c r="C2" s="31">
         <v>45482</v>
       </c>
-      <c r="D2" s="89">
-        <v>0.32851511169513797</v>
+      <c r="D2" s="87">
+        <v>0.46</v>
       </c>
       <c r="E2" s="32" t="s">
         <v>313</v>
@@ -12958,7 +13017,7 @@
       <c r="L2" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="99" t="s">
         <v>141</v>
       </c>
       <c r="N2" s="32" t="s">
@@ -12971,11 +13030,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>6.1403508771929821E-2</v>
       </c>
-      <c r="Q2" s="76">
+      <c r="Q2" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
-        <v>-1.1131724399994394</v>
-      </c>
-      <c r="R2" s="76">
+        <v>-0.77652878949899629</v>
+      </c>
+      <c r="R2" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-2.7587708079393853</v>
       </c>
@@ -12984,30 +13043,30 @@
       </c>
       <c r="T2" cm="1">
         <f t="array" ref="T2">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U2">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V2" cm="1">
         <f t="array" ref="V2">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W2">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X2" s="81">
+      <c r="X2" s="79">
         <f>EXP((-Tabela4[[#This Row],[b]])/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y2" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
       <c r="Z2" s="5">
         <f>Tabela4[[#This Row],[Prawdopodobieństwo wystąpienia awarii F(t)]]*Tabela3[[#This Row],[W rynku]]*(11/Tabela3[[#This Row],[W rynku]])</f>
-        <v>3.0930635738877044</v>
+        <v>4.4095937062102157</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -13020,7 +13079,7 @@
       <c r="C3" s="34">
         <v>45625</v>
       </c>
-      <c r="D3" s="90">
+      <c r="D3" s="88">
         <v>1.9382391590013099</v>
       </c>
       <c r="E3" s="35" t="s">
@@ -13047,7 +13106,7 @@
       <c r="L3" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M3" s="104" t="s">
         <v>165</v>
       </c>
       <c r="N3" s="35" t="s">
@@ -13060,11 +13119,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.14912280701754385</v>
       </c>
-      <c r="Q3" s="76">
+      <c r="Q3" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>0.66177991091223221</v>
       </c>
-      <c r="R3" s="76">
+      <c r="R3" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-1.8233277251429048</v>
       </c>
@@ -13073,26 +13132,26 @@
       </c>
       <c r="T3" cm="1">
         <f t="array" ref="T3">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U3">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V3" cm="1">
         <f t="array" ref="V3">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W3">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X3" s="81">
+      <c r="X3" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y3" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -13105,7 +13164,7 @@
       <c r="C4" s="34">
         <v>45107</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="88">
         <v>2.03679369250986</v>
       </c>
       <c r="E4" s="35" t="s">
@@ -13132,7 +13191,7 @@
       <c r="L4" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="103" t="s">
         <v>165</v>
       </c>
       <c r="N4" s="35" t="s">
@@ -13145,11 +13204,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.23684210526315791</v>
       </c>
-      <c r="Q4" s="76">
+      <c r="Q4" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>0.71137685205160872</v>
       </c>
-      <c r="R4" s="76">
+      <c r="R4" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-1.3082586023666756</v>
       </c>
@@ -13158,26 +13217,26 @@
       </c>
       <c r="T4" cm="1">
         <f t="array" ref="T4">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U4">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V4" cm="1">
         <f t="array" ref="V4">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W4">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X4" s="81">
+      <c r="X4" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y4" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -13190,19 +13249,19 @@
       <c r="C5" s="31">
         <v>45118</v>
       </c>
-      <c r="D5" s="89">
+      <c r="D5" s="87">
         <v>4.6649145860709602</v>
       </c>
       <c r="E5" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="37" t="s">
         <v>262</v>
       </c>
       <c r="I5" s="32" t="s">
@@ -13217,7 +13276,7 @@
       <c r="L5" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="39" t="s">
+      <c r="M5" s="106" t="s">
         <v>141</v>
       </c>
       <c r="N5" s="32" t="s">
@@ -13230,11 +13289,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.32456140350877194</v>
       </c>
-      <c r="Q5" s="76">
+      <c r="Q5" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.5400695246077758</v>
       </c>
-      <c r="R5" s="76">
+      <c r="R5" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.9354913227515631</v>
       </c>
@@ -13243,26 +13302,26 @@
       </c>
       <c r="T5" cm="1">
         <f t="array" ref="T5">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U5">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V5" cm="1">
         <f t="array" ref="V5">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W5">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X5" s="81">
+      <c r="X5" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y5" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -13275,7 +13334,7 @@
       <c r="C6" s="34">
         <v>45230</v>
       </c>
-      <c r="D6" s="90">
+      <c r="D6" s="88">
         <v>6.2746386333771396</v>
       </c>
       <c r="E6" s="35" t="s">
@@ -13315,11 +13374,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.41228070175438597</v>
       </c>
-      <c r="Q6" s="76">
+      <c r="Q6" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.8365158950531455</v>
       </c>
-      <c r="R6" s="76">
+      <c r="R6" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.63204111417931419</v>
       </c>
@@ -13328,26 +13387,26 @@
       </c>
       <c r="T6" cm="1">
         <f t="array" ref="T6">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U6">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V6" cm="1">
         <f t="array" ref="V6">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W6">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X6" s="81">
+      <c r="X6" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y6" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -13360,7 +13419,7 @@
       <c r="C7" s="34">
         <v>45015</v>
       </c>
-      <c r="D7" s="90">
+      <c r="D7" s="88">
         <v>6.7017082785808144</v>
       </c>
       <c r="E7" s="35" t="s">
@@ -13387,7 +13446,7 @@
       <c r="L7" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="103" t="s">
         <v>165</v>
       </c>
       <c r="N7" s="35" t="s">
@@ -13400,11 +13459,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.5</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.9023624608507312</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.36651292058166435</v>
       </c>
@@ -13413,26 +13472,26 @@
       </c>
       <c r="T7" cm="1">
         <f t="array" ref="T7">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U7">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V7" cm="1">
         <f t="array" ref="V7">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W7">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X7" s="81">
+      <c r="X7" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y7" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -13445,7 +13504,7 @@
       <c r="C8" s="31">
         <v>45135</v>
       </c>
-      <c r="D8" s="89">
+      <c r="D8" s="87">
         <v>12.582128777923783</v>
       </c>
       <c r="E8" s="32" t="s">
@@ -13472,7 +13531,7 @@
       <c r="L8" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="105" t="s">
         <v>165</v>
       </c>
       <c r="N8" s="32" t="s">
@@ -13485,11 +13544,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.58771929824561409</v>
       </c>
-      <c r="Q8" s="76">
+      <c r="Q8" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>2.5322774561871606</v>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.12098094098939045</v>
       </c>
@@ -13498,26 +13557,26 @@
       </c>
       <c r="T8" cm="1">
         <f t="array" ref="T8">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U8">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V8" cm="1">
         <f t="array" ref="V8">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W8">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X8" s="81">
+      <c r="X8" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y8" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -13530,19 +13589,19 @@
       <c r="C9" s="31">
         <v>44742</v>
       </c>
-      <c r="D9" s="89">
+      <c r="D9" s="87">
         <v>13.009198423127463</v>
       </c>
       <c r="E9" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="H9" s="38" t="s">
+      <c r="H9" s="37" t="s">
         <v>163</v>
       </c>
       <c r="I9" s="32" t="s">
@@ -13557,7 +13616,7 @@
       <c r="L9" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="102" t="s">
         <v>165</v>
       </c>
       <c r="N9" s="32" t="s">
@@ -13570,11 +13629,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.67543859649122806</v>
       </c>
-      <c r="Q9" s="76">
+      <c r="Q9" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>2.5656566782609955</v>
       </c>
-      <c r="R9" s="76">
+      <c r="R9" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.11803236968142394</v>
       </c>
@@ -13583,26 +13642,26 @@
       </c>
       <c r="T9" cm="1">
         <f t="array" ref="T9">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U9">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V9" cm="1">
         <f t="array" ref="V9">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W9">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X9" s="81">
+      <c r="X9" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y9" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -13615,7 +13674,7 @@
       <c r="C10" s="34">
         <v>44691</v>
       </c>
-      <c r="D10" s="90">
+      <c r="D10" s="88">
         <v>13.074901445466491</v>
       </c>
       <c r="E10" s="35" t="s">
@@ -13642,7 +13701,7 @@
       <c r="L10" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="98" t="s">
         <v>141</v>
       </c>
       <c r="N10" s="35" t="s">
@@ -13655,11 +13714,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.76315789473684204</v>
       </c>
-      <c r="Q10" s="76">
+      <c r="Q10" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>2.5706944722909526</v>
       </c>
-      <c r="R10" s="76">
+      <c r="R10" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.3648941809499211</v>
       </c>
@@ -13668,26 +13727,26 @@
       </c>
       <c r="T10" cm="1">
         <f t="array" ref="T10">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U10">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V10" cm="1">
         <f t="array" ref="V10">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W10">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X10" s="81">
+      <c r="X10" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y10" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -13700,7 +13759,7 @@
       <c r="C11" s="34">
         <v>45118</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="88">
         <v>21.911957950065702</v>
       </c>
       <c r="E11" s="35" t="s">
@@ -13727,7 +13786,7 @@
       <c r="L11" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="M11" s="35" t="s">
+      <c r="M11" s="100" t="s">
         <v>165</v>
       </c>
       <c r="N11" s="35" t="s">
@@ -13740,11 +13799,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.85087719298245601</v>
       </c>
-      <c r="Q11" s="76">
+      <c r="Q11" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>3.0870325129221388</v>
       </c>
-      <c r="R11" s="76">
+      <c r="R11" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.64342376082057084</v>
       </c>
@@ -13753,26 +13812,26 @@
       </c>
       <c r="T11" cm="1">
         <f t="array" ref="T11">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U11">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V11" cm="1">
         <f t="array" ref="V11">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W11">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X11" s="81">
+      <c r="X11" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y11" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -13785,7 +13844,7 @@
       <c r="C12" s="31">
         <v>45076</v>
       </c>
-      <c r="D12" s="89">
+      <c r="D12" s="87">
         <v>25.26281208935611</v>
       </c>
       <c r="E12" s="32" t="s">
@@ -13812,7 +13871,7 @@
       <c r="L12" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="101" t="s">
         <v>165</v>
       </c>
       <c r="N12" s="32" t="s">
@@ -13825,11 +13884,11 @@
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$12+0.4)</f>
         <v>0.9385964912280701</v>
       </c>
-      <c r="Q12" s="76">
+      <c r="Q12" s="74">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>3.2293334365121589</v>
       </c>
-      <c r="R12" s="76">
+      <c r="R12" s="74">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>1.0261449235912583</v>
       </c>
@@ -13838,154 +13897,154 @@
       </c>
       <c r="T12" cm="1">
         <f t="array" ref="T12">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>0.86</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="U12">
         <v>-2.0529999999999999</v>
       </c>
       <c r="V12" cm="1">
         <f t="array" ref="V12">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
-        <v>-2.0529999999999999</v>
+        <v>-2.1821000000000002</v>
       </c>
       <c r="W12">
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.86</v>
       </c>
-      <c r="X12" s="81">
+      <c r="X12" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>10.883080138480715</v>
       </c>
       <c r="Y12" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.28118759762615497</v>
+        <v>0.40087215511001961</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="40">
+      <c r="A13" s="38">
         <v>1</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="39">
         <v>45741</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="39">
         <v>45089</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="89">
         <v>21.419185282522996</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="40" t="s">
         <v>325</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="40" t="s">
         <v>262</v>
       </c>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J13" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="K13" s="42" t="s">
+      <c r="K13" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="L13" s="42" t="s">
+      <c r="L13" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="N13" s="42" t="s">
+      <c r="N13" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="O13" s="42" t="s">
+      <c r="O13" s="40" t="s">
         <v>327</v>
       </c>
-      <c r="P13" s="75">
+      <c r="P13" s="73">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$13+0.4)</f>
         <v>0.5</v>
       </c>
-      <c r="Q13" s="77">
+      <c r="Q13" s="75">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>3.0642870289331681</v>
       </c>
-      <c r="R13" s="77">
+      <c r="R13" s="75">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.36651292058166435</v>
       </c>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77" t="e" cm="1">
+      <c r="S13" s="75"/>
+      <c r="T13" s="75" t="e" cm="1">
         <f t="array" ref="T13">ROUND(SLOPE(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U13" s="77"/>
-      <c r="V13" s="77" t="e" cm="1">
+      <c r="U13" s="75"/>
+      <c r="V13" s="75" t="e" cm="1">
         <f t="array" ref="V13">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X13" s="81"/>
+      <c r="X13" s="79"/>
       <c r="Y13" s="5"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
+      <c r="A14" s="41">
         <v>1</v>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="42">
         <v>45138</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="42">
         <v>45117</v>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="90">
         <v>0.68988173455978974</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="43" t="s">
         <v>367</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="44" t="s">
         <v>368</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="44" t="s">
         <v>369</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="44" t="s">
         <v>370</v>
       </c>
-      <c r="I14" s="45" t="s">
+      <c r="I14" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="45" t="s">
+      <c r="J14" s="43" t="s">
         <v>371</v>
       </c>
-      <c r="K14" s="45" t="s">
+      <c r="K14" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L14" s="45" t="s">
+      <c r="L14" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="47" t="s">
+      <c r="M14" s="45" t="s">
         <v>365</v>
       </c>
-      <c r="N14" s="45" t="s">
+      <c r="N14" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="45" t="s">
+      <c r="O14" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P14" s="72">
+      <c r="P14" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>9.4594594594594586E-2</v>
       </c>
-      <c r="Q14" s="78">
+      <c r="Q14" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>-0.3712350952700621</v>
       </c>
-      <c r="R14" s="78">
+      <c r="R14" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-2.3088801270783894</v>
       </c>
@@ -14007,74 +14066,74 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X14" s="81">
+      <c r="X14" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y14" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
-      </c>
-      <c r="Z14" s="81">
+        <v>0.4982562004362503</v>
+      </c>
+      <c r="Z14" s="79">
         <f>Tabela4[[#This Row],[Prawdopodobieństwo wystąpienia awarii F(t)]]*7</f>
-        <v>2.5777925768575716</v>
+        <v>3.4877934030537521</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
+      <c r="A15" s="41">
         <v>2</v>
       </c>
-      <c r="B15" s="48">
+      <c r="B15" s="46">
         <v>45138</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="46">
         <v>45096</v>
       </c>
-      <c r="D15" s="93">
+      <c r="D15" s="91">
         <v>1.3797634691195795</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="H15" s="50" t="s">
+      <c r="H15" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="I15" s="49" t="s">
+      <c r="I15" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="J15" s="49" t="s">
+      <c r="J15" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="K15" s="49" t="s">
+      <c r="K15" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="L15" s="49" t="s">
+      <c r="L15" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="51" t="s">
+      <c r="M15" s="49" t="s">
         <v>365</v>
       </c>
-      <c r="N15" s="49" t="s">
+      <c r="N15" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="45" t="s">
+      <c r="O15" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P15" s="72">
+      <c r="P15" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>0.22972972972972971</v>
       </c>
-      <c r="Q15" s="78">
+      <c r="Q15" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>0.32191208528988319</v>
       </c>
-      <c r="R15" s="78">
+      <c r="R15" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-1.3431819022975191</v>
       </c>
@@ -14096,70 +14155,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X15" s="81">
+      <c r="X15" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y15" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
+        <v>0.4982562004362503</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
+      <c r="A16" s="41">
         <v>3</v>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="46">
         <v>45138</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="46">
         <v>45075</v>
       </c>
-      <c r="D16" s="93">
+      <c r="D16" s="91">
         <v>2.0696452036793693</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="47" t="s">
         <v>223</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="48" t="s">
         <v>345</v>
       </c>
-      <c r="H16" s="50" t="s">
+      <c r="H16" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="I16" s="49" t="s">
+      <c r="I16" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="49" t="s">
+      <c r="J16" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="K16" s="49" t="s">
+      <c r="K16" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="L16" s="49" t="s">
+      <c r="L16" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="M16" s="51" t="s">
+      <c r="M16" s="49" t="s">
         <v>346</v>
       </c>
-      <c r="N16" s="49" t="s">
+      <c r="N16" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P16" s="72">
+      <c r="P16" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>0.36486486486486486</v>
       </c>
-      <c r="Q16" s="78">
+      <c r="Q16" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>0.72737719339804763</v>
       </c>
-      <c r="R16" s="78">
+      <c r="R16" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.78983983425403359</v>
       </c>
@@ -14181,70 +14240,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X16" s="81">
+      <c r="X16" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y16" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
+        <v>0.4982562004362503</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
+      <c r="A17" s="41">
         <v>4</v>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="42">
         <v>45169</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="42">
         <v>45015</v>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="90">
         <v>5.0591327201051248</v>
       </c>
-      <c r="E17" s="45" t="s">
+      <c r="E17" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="G17" s="46" t="s">
+      <c r="G17" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="I17" s="45" t="s">
+      <c r="I17" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="45" t="s">
+      <c r="J17" s="43" t="s">
         <v>338</v>
       </c>
-      <c r="K17" s="45" t="s">
+      <c r="K17" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L17" s="45" t="s">
+      <c r="L17" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="M17" s="47" t="s">
+      <c r="M17" s="45" t="s">
         <v>339</v>
       </c>
-      <c r="N17" s="45" t="s">
+      <c r="N17" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="O17" s="45" t="s">
+      <c r="O17" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P17" s="72">
+      <c r="P17" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>0.5</v>
       </c>
-      <c r="Q17" s="78">
+      <c r="Q17" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.621195069420144</v>
       </c>
-      <c r="R17" s="78">
+      <c r="R17" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.36651292058166435</v>
       </c>
@@ -14266,70 +14325,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X17" s="81">
+      <c r="X17" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y17" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
+        <v>0.4982562004362503</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+      <c r="A18" s="41">
         <v>5</v>
       </c>
-      <c r="B18" s="44">
+      <c r="B18" s="42">
         <v>45260</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="42">
         <v>45098</v>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="90">
         <v>5.3219448094612352</v>
       </c>
-      <c r="E18" s="45" t="s">
+      <c r="E18" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="44" t="s">
         <v>261</v>
       </c>
-      <c r="H18" s="46" t="s">
+      <c r="H18" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="I18" s="45" t="s">
+      <c r="I18" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J18" s="45" t="s">
+      <c r="J18" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="K18" s="45" t="s">
+      <c r="K18" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L18" s="45" t="s">
+      <c r="L18" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="M18" s="47" t="s">
+      <c r="M18" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="N18" s="45" t="s">
+      <c r="N18" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="O18" s="45" t="s">
+      <c r="O18" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P18" s="72">
+      <c r="P18" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>0.63513513513513509</v>
       </c>
-      <c r="Q18" s="78">
+      <c r="Q18" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.671838802238899</v>
       </c>
-      <c r="R18" s="78">
+      <c r="R18" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>8.1945598938292404E-3</v>
       </c>
@@ -14351,70 +14410,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X18" s="81">
+      <c r="X18" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y18" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
+        <v>0.4982562004362503</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="43">
+      <c r="A19" s="41">
         <v>6</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="46">
         <v>45796</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="46">
         <v>45181</v>
       </c>
-      <c r="D19" s="93">
+      <c r="D19" s="91">
         <v>20.203679369250985</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="47" t="s">
         <v>373</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="47" t="s">
         <v>374</v>
       </c>
-      <c r="G19" s="49" t="s">
+      <c r="G19" s="47" t="s">
         <v>375</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="49" t="s">
+      <c r="J19" s="47" t="s">
         <v>377</v>
       </c>
-      <c r="K19" s="49" t="s">
+      <c r="K19" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="L19" s="49" t="s">
+      <c r="L19" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="M19" s="49" t="s">
+      <c r="M19" s="47" t="s">
         <v>365</v>
       </c>
-      <c r="N19" s="49" t="s">
+      <c r="N19" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="O19" s="45" t="s">
+      <c r="O19" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P19" s="72">
+      <c r="P19" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>0.77027027027027029</v>
       </c>
-      <c r="Q19" s="78">
+      <c r="Q19" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>3.005864734813033</v>
       </c>
-      <c r="R19" s="78">
+      <c r="R19" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.38584165418008665</v>
       </c>
@@ -14436,70 +14495,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X19" s="81">
+      <c r="X19" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y19" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
+        <v>0.4982562004362503</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
+      <c r="A20" s="41">
         <v>7</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="42">
         <v>45684</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="42">
         <v>45016</v>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="90">
         <v>21.944809461235216</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="43" t="s">
         <v>320</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="G20" s="43" t="s">
         <v>321</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="43" t="s">
         <v>322</v>
       </c>
-      <c r="I20" s="45" t="s">
+      <c r="I20" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="45" t="s">
+      <c r="J20" s="43" t="s">
         <v>323</v>
       </c>
-      <c r="K20" s="45" t="s">
+      <c r="K20" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="L20" s="45" t="s">
+      <c r="L20" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="M20" s="45" t="s">
+      <c r="M20" s="43" t="s">
         <v>343</v>
       </c>
-      <c r="N20" s="45" t="s">
+      <c r="N20" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="O20" s="45" t="s">
+      <c r="O20" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="P20" s="72">
+      <c r="P20" s="70">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$20+0.4)</f>
         <v>0.90540540540540537</v>
       </c>
-      <c r="Q20" s="78">
+      <c r="Q20" s="76">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>3.0885306405431607</v>
       </c>
-      <c r="R20" s="78">
+      <c r="R20" s="76">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.85787950994316486</v>
       </c>
@@ -14521,70 +14580,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>0.79590000000000005</v>
       </c>
-      <c r="X20" s="81">
+      <c r="X20" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.9746348640093805</v>
       </c>
       <c r="Y20" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.36825608240822449</v>
+        <v>0.4982562004362503</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="52">
+      <c r="A21" s="50">
         <v>1</v>
       </c>
-      <c r="B21" s="53">
+      <c r="B21" s="51">
         <v>45289</v>
       </c>
-      <c r="C21" s="53">
+      <c r="C21" s="51">
         <v>45229</v>
       </c>
-      <c r="D21" s="94">
+      <c r="D21" s="92">
         <v>1.9710906701708277</v>
       </c>
-      <c r="E21" s="54" t="s">
+      <c r="E21" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="55" t="s">
+      <c r="F21" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="55" t="s">
+      <c r="G21" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="55" t="s">
+      <c r="H21" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="I21" s="54" t="s">
+      <c r="I21" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="54" t="s">
+      <c r="J21" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="K21" s="54" t="s">
+      <c r="K21" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="54" t="s">
+      <c r="L21" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="M21" s="56" t="s">
+      <c r="M21" s="54" t="s">
         <v>403</v>
       </c>
-      <c r="N21" s="54" t="s">
+      <c r="N21" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="O21" s="54" t="s">
+      <c r="O21" s="52" t="s">
         <v>404</v>
       </c>
-      <c r="P21" s="73">
+      <c r="P21" s="71">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$22+0.4)</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="Q21" s="79">
+      <c r="Q21" s="77">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>0.67858702922861558</v>
       </c>
-      <c r="R21" s="79">
+      <c r="R21" s="77">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-1.0646733274461582</v>
       </c>
@@ -14598,64 +14657,64 @@
         <f t="array" ref="V21">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
         <v>-2.1303000000000001</v>
       </c>
-      <c r="X21" s="81"/>
+      <c r="X21" s="79"/>
       <c r="Y21" s="5"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="52">
+      <c r="A22" s="50">
         <v>2</v>
       </c>
-      <c r="B22" s="57">
+      <c r="B22" s="55">
         <v>45169</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="55">
         <v>45034</v>
       </c>
-      <c r="D22" s="95">
+      <c r="D22" s="93">
         <v>4.4349540078843628</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="56" t="s">
         <v>405</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="57" t="s">
         <v>406</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="57" t="s">
         <v>407</v>
       </c>
-      <c r="H22" s="59" t="s">
+      <c r="H22" s="57" t="s">
         <v>408</v>
       </c>
-      <c r="I22" s="58" t="s">
+      <c r="I22" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="J22" s="58" t="s">
+      <c r="J22" s="56" t="s">
         <v>409</v>
       </c>
-      <c r="K22" s="58" t="s">
+      <c r="K22" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="L22" s="58" t="s">
+      <c r="L22" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="60" t="s">
+      <c r="M22" s="58" t="s">
         <v>410</v>
       </c>
-      <c r="N22" s="58" t="s">
+      <c r="N22" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="O22" s="58" t="s">
+      <c r="O22" s="56" t="s">
         <v>404</v>
       </c>
-      <c r="P22" s="73">
+      <c r="P22" s="71">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$22+0.4)</f>
         <v>0.70833333333333337</v>
       </c>
-      <c r="Q22" s="79">
+      <c r="Q22" s="77">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.4895172454449443</v>
       </c>
-      <c r="R22" s="79">
+      <c r="R22" s="77">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.20875548273706646</v>
       </c>
@@ -14669,64 +14728,64 @@
         <f t="array" ref="V22">ROUND(INTERCEPT(_xlfn._xlws.FILTER(Tabela4[Y],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]]),_xlfn._xlws.FILTER(Tabela4[X],$O$2:$O$26=Tabela4[[#This Row],[Base GroupB Cn]])),4)</f>
         <v>-2.1303000000000001</v>
       </c>
-      <c r="X22" s="81"/>
+      <c r="X22" s="79"/>
       <c r="Y22" s="5"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="61">
+      <c r="A23" s="59">
         <v>1</v>
       </c>
-      <c r="B23" s="62">
+      <c r="B23" s="60">
         <v>45230</v>
       </c>
-      <c r="C23" s="62">
+      <c r="C23" s="60">
         <v>45169</v>
       </c>
-      <c r="D23" s="96">
+      <c r="D23" s="94">
         <v>2.0039421813403417</v>
       </c>
-      <c r="E23" s="63" t="s">
+      <c r="E23" s="61" t="s">
         <v>439</v>
       </c>
-      <c r="F23" s="64" t="s">
+      <c r="F23" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="62" t="s">
         <v>440</v>
       </c>
-      <c r="H23" s="64" t="s">
+      <c r="H23" s="62" t="s">
         <v>441</v>
       </c>
-      <c r="I23" s="63" t="s">
+      <c r="I23" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="63" t="s">
+      <c r="J23" s="61" t="s">
         <v>442</v>
       </c>
-      <c r="K23" s="63" t="s">
+      <c r="K23" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="L23" s="63" t="s">
+      <c r="L23" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="M23" s="65" t="s">
+      <c r="M23" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="N23" s="63" t="s">
+      <c r="N23" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="O23" s="63" t="s">
+      <c r="O23" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="P23" s="74">
+      <c r="P23" s="72">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$26+0.4)</f>
         <v>0.15909090909090906</v>
       </c>
-      <c r="Q23" s="80">
+      <c r="Q23" s="78">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>0.69511633117982619</v>
       </c>
-      <c r="R23" s="80">
+      <c r="R23" s="78">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-1.752894273451838</v>
       </c>
@@ -14748,74 +14807,74 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>1.3684000000000001</v>
       </c>
-      <c r="X23" s="81">
+      <c r="X23" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.5170467478646685</v>
       </c>
       <c r="Y23" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.24762314769678773</v>
-      </c>
-      <c r="Z23" s="81">
+        <v>0.43582117575685053</v>
+      </c>
+      <c r="Z23" s="5">
         <f>Tabela4[[#This Row],[Prawdopodobieństwo wystąpienia awarii F(t)]]*4</f>
-        <v>0.99049259078715091</v>
+        <v>1.7432847030274021</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="61">
+      <c r="A24" s="59">
         <v>2</v>
       </c>
-      <c r="B24" s="66">
+      <c r="B24" s="64">
         <v>45230</v>
       </c>
-      <c r="C24" s="66">
+      <c r="C24" s="64">
         <v>45064</v>
       </c>
-      <c r="D24" s="97">
+      <c r="D24" s="95">
         <v>5.4533508541392903</v>
       </c>
-      <c r="E24" s="67" t="s">
+      <c r="E24" s="65" t="s">
         <v>435</v>
       </c>
-      <c r="F24" s="68" t="s">
+      <c r="F24" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="66" t="s">
         <v>436</v>
       </c>
-      <c r="H24" s="68" t="s">
+      <c r="H24" s="66" t="s">
         <v>437</v>
       </c>
-      <c r="I24" s="67" t="s">
+      <c r="I24" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="J24" s="67" t="s">
+      <c r="J24" s="65" t="s">
         <v>438</v>
       </c>
-      <c r="K24" s="67" t="s">
+      <c r="K24" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="L24" s="67" t="s">
+      <c r="L24" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="M24" s="69" t="s">
+      <c r="M24" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="N24" s="67" t="s">
+      <c r="N24" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="O24" s="67" t="s">
+      <c r="O24" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="P24" s="74">
+      <c r="P24" s="72">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$26+0.4)</f>
         <v>0.3863636363636363</v>
       </c>
-      <c r="Q24" s="80">
+      <c r="Q24" s="78">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.6962302553630582</v>
       </c>
-      <c r="R24" s="80">
+      <c r="R24" s="78">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-0.71671724921501978</v>
       </c>
@@ -14837,70 +14896,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>1.3684000000000001</v>
       </c>
-      <c r="X24" s="81">
+      <c r="X24" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.5170467478646685</v>
       </c>
       <c r="Y24" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.24762314769678773</v>
+        <v>0.43582117575685053</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="61">
+      <c r="A25" s="59">
         <v>3</v>
       </c>
-      <c r="B25" s="66">
+      <c r="B25" s="64">
         <v>45289</v>
       </c>
-      <c r="C25" s="66">
+      <c r="C25" s="64">
         <v>45096</v>
       </c>
-      <c r="D25" s="97">
+      <c r="D25" s="95">
         <v>6.3403416557161627</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="65" t="s">
         <v>447</v>
       </c>
-      <c r="F25" s="68" t="s">
+      <c r="F25" s="66" t="s">
         <v>448</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="G25" s="66" t="s">
         <v>449</v>
       </c>
-      <c r="H25" s="68" t="s">
+      <c r="H25" s="66" t="s">
         <v>450</v>
       </c>
-      <c r="I25" s="67" t="s">
+      <c r="I25" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="J25" s="67" t="s">
+      <c r="J25" s="65" t="s">
         <v>451</v>
       </c>
-      <c r="K25" s="67" t="s">
+      <c r="K25" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="67" t="s">
+      <c r="L25" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="M25" s="69" t="s">
+      <c r="M25" s="67" t="s">
         <v>452</v>
       </c>
-      <c r="N25" s="67" t="s">
+      <c r="N25" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="O25" s="67" t="s">
+      <c r="O25" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="P25" s="74">
+      <c r="P25" s="72">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$26+0.4)</f>
         <v>0.61363636363636365</v>
       </c>
-      <c r="Q25" s="80">
+      <c r="Q25" s="78">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>1.8469326559114003</v>
       </c>
-      <c r="R25" s="80">
+      <c r="R25" s="78">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>-5.0266148543505945E-2</v>
       </c>
@@ -14922,70 +14981,70 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>1.3684000000000001</v>
       </c>
-      <c r="X25" s="81">
+      <c r="X25" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.5170467478646685</v>
       </c>
       <c r="Y25" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.24762314769678773</v>
+        <v>0.43582117575685053</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="61">
+      <c r="A26" s="59">
         <v>4</v>
       </c>
-      <c r="B26" s="70">
+      <c r="B26" s="68">
         <v>45559</v>
       </c>
-      <c r="C26" s="70">
+      <c r="C26" s="68">
         <v>45212</v>
       </c>
-      <c r="D26" s="98">
+      <c r="D26" s="96">
         <v>11.399474375821287</v>
       </c>
-      <c r="E26" s="71" t="s">
+      <c r="E26" s="69" t="s">
         <v>468</v>
       </c>
-      <c r="F26" s="71" t="s">
+      <c r="F26" s="69" t="s">
         <v>469</v>
       </c>
-      <c r="G26" s="71" t="s">
+      <c r="G26" s="69" t="s">
         <v>470</v>
       </c>
-      <c r="H26" s="71" t="s">
+      <c r="H26" s="69" t="s">
         <v>471</v>
       </c>
-      <c r="I26" s="71" t="s">
+      <c r="I26" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="J26" s="71" t="s">
+      <c r="J26" s="69" t="s">
         <v>472</v>
       </c>
-      <c r="K26" s="71" t="s">
+      <c r="K26" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="L26" s="71" t="s">
+      <c r="L26" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="71" t="s">
+      <c r="M26" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="N26" s="71" t="s">
+      <c r="N26" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="O26" s="71" t="s">
+      <c r="O26" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="P26" s="74">
+      <c r="P26" s="72">
         <f>(Tabela4[[#This Row],[Nr porządkowy]]-0.3)/($A$26+0.4)</f>
         <v>0.84090909090909083</v>
       </c>
-      <c r="Q26" s="80">
+      <c r="Q26" s="78">
         <f>LN(Tabela4[[#This Row],[Czas do awarii Ti]])</f>
         <v>2.4335672469533738</v>
       </c>
-      <c r="R26" s="80">
+      <c r="R26" s="78">
         <f>LN(-LN(1-Tabela4[[#This Row],[Empiryczne prawdopodobieństwo awarii (Fi)]]))</f>
         <v>0.60883007160268721</v>
       </c>
@@ -15007,13 +15066,13 @@
         <f>Tabela4[[#This Row],[a]]</f>
         <v>1.3684000000000001</v>
       </c>
-      <c r="X26" s="81">
+      <c r="X26" s="79">
         <f>EXP(-Tabela4[[#This Row],[b]]/Tabela4[[#This Row],[a]])</f>
         <v>7.5170467478646685</v>
       </c>
       <c r="Y26" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela4[[#This Row],[η]])^Tabela4[[#This Row],[ß]]))</f>
-        <v>0.24762314769678773</v>
+        <v>0.43582117575685053</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
@@ -15129,10 +15188,10 @@
       <c r="W1" s="28" t="s">
         <v>547</v>
       </c>
-      <c r="Y1" s="87" t="s">
+      <c r="Y1" s="85" t="s">
         <v>541</v>
       </c>
-      <c r="Z1" s="87" t="s">
+      <c r="Z1" s="85" t="s">
         <v>543</v>
       </c>
     </row>
@@ -15210,12 +15269,12 @@
       </c>
       <c r="W2" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
-      </c>
-      <c r="Y2" s="88">
+        <v>0.31113507357990045</v>
+      </c>
+      <c r="Y2" s="86">
         <v>1.022</v>
       </c>
-      <c r="Z2" s="88">
+      <c r="Z2" s="86">
         <v>-2.6318000000000001</v>
       </c>
     </row>
@@ -15293,7 +15352,7 @@
       </c>
       <c r="W3" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -15370,7 +15429,7 @@
       </c>
       <c r="W4" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -15447,7 +15506,7 @@
       </c>
       <c r="W5" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -15524,7 +15583,7 @@
       </c>
       <c r="W6" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -15601,7 +15660,7 @@
       </c>
       <c r="W7" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -15678,7 +15737,7 @@
       </c>
       <c r="W8" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -15755,7 +15814,7 @@
       </c>
       <c r="W9" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -15832,7 +15891,7 @@
       </c>
       <c r="W10" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -15909,7 +15968,7 @@
       </c>
       <c r="W11" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -15986,7 +16045,7 @@
       </c>
       <c r="W12" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -16063,7 +16122,7 @@
       </c>
       <c r="W13" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -16140,7 +16199,7 @@
       </c>
       <c r="W14" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -16217,7 +16276,7 @@
       </c>
       <c r="W15" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -16294,7 +16353,7 @@
       </c>
       <c r="W16" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
@@ -16371,7 +16430,7 @@
       </c>
       <c r="W17" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
@@ -16448,7 +16507,7 @@
       </c>
       <c r="W18" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
@@ -16525,7 +16584,7 @@
       </c>
       <c r="W19" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
@@ -16602,7 +16661,7 @@
       </c>
       <c r="W20" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
@@ -16679,7 +16738,7 @@
       </c>
       <c r="W21" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
@@ -16756,7 +16815,7 @@
       </c>
       <c r="W22" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
@@ -16833,7 +16892,7 @@
       </c>
       <c r="W23" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
@@ -16910,7 +16969,7 @@
       </c>
       <c r="W24" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
@@ -16987,7 +17046,7 @@
       </c>
       <c r="W25" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
@@ -17064,7 +17123,7 @@
       </c>
       <c r="W26" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
@@ -17141,7 +17200,7 @@
       </c>
       <c r="W27" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
@@ -17218,7 +17277,7 @@
       </c>
       <c r="W28" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
@@ -17295,7 +17354,7 @@
       </c>
       <c r="W29" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
@@ -17372,7 +17431,7 @@
       </c>
       <c r="W30" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
@@ -17449,7 +17508,7 @@
       </c>
       <c r="W31" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
@@ -17526,7 +17585,7 @@
       </c>
       <c r="W32" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -17603,7 +17662,7 @@
       </c>
       <c r="W33" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -17680,7 +17739,7 @@
       </c>
       <c r="W34" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
@@ -17757,7 +17816,7 @@
       </c>
       <c r="W35" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
@@ -17834,7 +17893,7 @@
       </c>
       <c r="W36" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
@@ -17911,7 +17970,7 @@
       </c>
       <c r="W37" s="5">
         <f>1-EXP(-(('dane źródłowe'!$C$9/Tabela2[[#This Row],[η]])^Tabela2[[#This Row],[ß]]))</f>
-        <v>0.1983851030618663</v>
+        <v>0.31113507357990045</v>
       </c>
     </row>
   </sheetData>

--- a/Obszar testowy/Awaryjność/kalkulacja Blanc PRO.xlsx
+++ b/Obszar testowy/Awaryjność/kalkulacja Blanc PRO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ReportsBI\Obszar testowy\Awaryjność\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FC7A11-F9EA-41AF-A12F-FD7092598FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C861D304-0CD3-4C4A-A890-EE4A4636FED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="źródła danych" sheetId="8" r:id="rId1"/>
@@ -15115,7 +15115,7 @@
     <col min="15" max="15" width="9.85546875" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="19.140625" customWidth="1"/>
     <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.7109375" customWidth="1"/>
+    <col min="23" max="23" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -17988,6 +17988,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0d6c5dbd-25b1-4fbf-83f9-b289d7b111a0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3fec9504-7640-4451-840c-8d09d21130e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010053AB71B891A2544DBD445D04ABE7886B" ma:contentTypeVersion="11" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="323ef943dc9fb95ca33ee9e1c20c1484">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0d6c5dbd-25b1-4fbf-83f9-b289d7b111a0" xmlns:ns3="3fec9504-7640-4451-840c-8d09d21130e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fa2476893f5436c76bf320e2ff6b1281" ns2:_="" ns3:_="">
     <xsd:import namespace="0d6c5dbd-25b1-4fbf-83f9-b289d7b111a0"/>
@@ -18182,27 +18202,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0d6c5dbd-25b1-4fbf-83f9-b289d7b111a0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3fec9504-7640-4451-840c-8d09d21130e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DFC4402-E35E-46FF-8848-81414920BC84}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5150075-143E-4EB1-BF6D-1F0C09ED3DE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0d6c5dbd-25b1-4fbf-83f9-b289d7b111a0"/>
+    <ds:schemaRef ds:uri="3fec9504-7640-4451-840c-8d09d21130e6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC7D9EEB-D65E-44A8-BCF5-7663D46C9A1A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18219,23 +18238,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5150075-143E-4EB1-BF6D-1F0C09ED3DE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0d6c5dbd-25b1-4fbf-83f9-b289d7b111a0"/>
-    <ds:schemaRef ds:uri="3fec9504-7640-4451-840c-8d09d21130e6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DFC4402-E35E-46FF-8848-81414920BC84}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>